--- a/maintenance/MiniCapstan_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/MiniCapstan_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,26 @@
           <t>Last_Done_Draw</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +633,22 @@
         <v>0</v>
       </c>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -698,6 +734,22 @@
         <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Light machine oil; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/maintenance/MiniCapstan_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/MiniCapstan_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,21 @@
           <t>Estimated duration min</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,9 +609,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Mini Capstan (SG Controls)</t>
@@ -620,19 +632,20 @@
           <t>Trap and crush hazard due to rotating and pneumatically actuated rollers. Wear eye protection and ensure no loose clothing or jewellery.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U2" t="n">
+        <v>93</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>IPA wipes / cleaning cloth</t>
@@ -648,6 +661,15 @@
       </c>
       <c r="Y2" t="n">
         <v>30</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +711,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>weeks</t>
@@ -721,19 +742,14 @@
           <t>Working at height precautions apply. Do not over-lubricate; remove excess oil.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
+          <t>2026-04-02</t>
+        </is>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Light machine oil; IPA wipes / cleaning cloth</t>
